--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/oct-2025.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/oct-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC oct-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC oct-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12688,7 +12688,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13542,7 +13542,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/oct-2025.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/oct-2025.xlsx
@@ -562,7 +562,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +810,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +875,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +940,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1005,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1314,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1379,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1505,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1936,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2184,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2310,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2497,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2562,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2810,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2875,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3001,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3310,11 @@
           <t>76.359.833-0</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3436,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3562,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3688,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3875,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +3940,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4005,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4070,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4196,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4322,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4387,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4452,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4517,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4643,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4708,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4773,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5021,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5208,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5456,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5582,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5708,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5834,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6021,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6086,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6212,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6277,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6342,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6407,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6472,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6720,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6785,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7094,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7159,11 @@
           <t>77.721.515-9</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7285,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7411,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7476,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7541,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7606,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8220,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8285,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8411,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8476,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +8846,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +8911,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9220,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9285,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9411,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9659,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +9785,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +9972,11 @@
           <t>77.820.166-6</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10037,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10224,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10350,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10476,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +10785,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +10850,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +10915,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11041,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11106,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11171,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11297,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11362,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11610,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12041,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12106,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12171,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +12785,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +12850,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +12915,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +12980,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13167,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13598,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13663,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +13789,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +13854,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +13919,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14045,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
